--- a/assets/template_upload_stock_distributor.xlsx
+++ b/assets/template_upload_stock_distributor.xlsx
@@ -1,47 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="120" windowWidth="18060" windowHeight="7050" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Selected Parameters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="[$-010809]#,##0;-#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-010809]#,##0.00;-#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$-010809]#,0.00;(#,0.00);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="[$-010809]dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font/>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="10"/>
+      <strike val="0"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <name val="Calibri"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +75,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FF9DD11C"/>
+        <bgColor rgb="FF9DD11C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF008080"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -63,20 +94,196 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC0C0C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC0C0C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC0C0C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC0C0C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC0C0C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC0C0C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC0C0C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC0C0C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC0C0C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC0C0C0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC0C0C0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -90,10 +297,10 @@
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="0000FFFF"/>
       <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="009DD11C"/>
       <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00008080"/>
       <rgbColor rgb="00FFFF00"/>
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="0000FFFF"/>
@@ -102,8 +309,8 @@
       <rgbColor rgb="00000080"/>
       <rgbColor rgb="00808000"/>
       <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000FF00"/>
       <rgbColor rgb="00808080"/>
       <rgbColor rgb="009999FF"/>
       <rgbColor rgb="00993366"/>
@@ -436,204 +643,2003 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8.6640625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="17.4140625" customWidth="1" style="24" min="2" max="2"/>
+    <col width="10.5625" customWidth="1" style="24" min="3" max="3"/>
+    <col width="10.140625" customWidth="1" style="24" min="4" max="4"/>
+    <col width="6.2421875" customWidth="1" style="24" min="5" max="5"/>
+    <col width="6.23046875" customWidth="1" style="24" min="6" max="6"/>
+    <col width="6.23046875" customWidth="1" style="24" min="7" max="7"/>
+    <col width="9.2734375" customWidth="1" style="24" min="8" max="8"/>
+    <col width="6.8515625" customWidth="1" style="24" min="9" max="9"/>
+    <col width="11.3828125" customWidth="1" style="24" min="10" max="10"/>
+    <col width="11.203125" customWidth="1" style="24" min="11" max="11"/>
+    <col width="10.9609375" customWidth="1" style="24" min="12" max="12"/>
+    <col width="0.0234375" customWidth="1" style="24" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="0.3" customHeight="1" s="24"/>
+    <row r="2" ht="6.85" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>PCODE</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>NAMA BARANG</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ISI</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Nama Barang</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Isi Per Karton
+PCs</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ON CUST.ORDER</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Gudang Utama</t>
         </is>
       </c>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>RPP 13 Pkn
+Karton</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>WK.
+COVER</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Nilai.RP.Jual</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Nilai.RP.Beli</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>MAP (RP)</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
-      <c r="D2" s="1" t="inlineStr">
+    <row r="3" ht="6.85" customHeight="1" s="24">
+      <c r="A3" s="27" t="n"/>
+      <c r="B3" s="27" t="n"/>
+      <c r="C3" s="27" t="n"/>
+      <c r="D3" s="27" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Karton</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Lusin</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>PCs</t>
         </is>
       </c>
+      <c r="H3" s="27" t="n"/>
+      <c r="I3" s="27" t="n"/>
+      <c r="J3" s="27" t="n"/>
+      <c r="K3" s="27" t="n"/>
+      <c r="L3" s="27" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>64840063</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>DOVE DEEPLY NOURISH PUMP RL 6X2X550ML</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="n">
+    <row r="4" ht="6.85" customHeight="1" s="24">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>67656898</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ROYCO CREAM OF CRAB &amp; CORN 48X44GR</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>48</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="6.9" customHeight="1" s="24">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>64378615</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ROYCO MUSHROOM 24X170G RL3</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="6.85" customHeight="1" s="24">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>64862442</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ROYCO FDS CHICKEN RLC4 576X8G</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>576</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="6.85" customHeight="1" s="24">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>64862445</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ROYCO FDS BEEF RLC4 576X8G</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>576</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>41</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="6.85" customHeight="1" s="24">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>64873190</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ROYCO BEEF RL2 24X220G</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="6.85" customHeight="1" s="24">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>64873191</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ROYCO FDS CHICKEN RL3 24X220G</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="6.85" customHeight="1" s="24">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>64873193</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ROYCO FDS BEEF RL2 MP 40X(6X8G)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="6.85" customHeight="1" s="24">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>64873195</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ROYCO FDS CHICKEN MP RL3 40X(6X8G)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="6.9" customHeight="1" s="24">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>64873198</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ROYCO FDS BEEF RL2 36X94G</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>36</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>3</v>
+      <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>69965241</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>VASELINE HB SPF30 PPF VIT SRM 8X3X180ML</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+    <row r="13" ht="6.85" customHeight="1" s="24">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>64958615</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ROYCO FDS FISH 288X8G</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>288</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="6.85" customHeight="1" s="24">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>65549503</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ROYCO CHICKEN FREE FISH 24X(220+8)G</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>6</v>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>69794123</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>VASELINE HB SOFT GLOW VIT SRM 2X6X180ML</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="n">
+    <row r="15" ht="6.85" customHeight="1" s="24">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>65641404</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ROYCO BANDED BEEF+FISH 8X(72X8G)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>65085559</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>VIXAL KUAT SEGAR BKC PCH 12X600ML</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
+    <row r="16" ht="6.85" customHeight="1" s="24"/>
+    <row r="17" ht="6.85" customHeight="1" s="24"/>
+    <row r="18" ht="6.85" customHeight="1" s="24"/>
+    <row r="19" ht="6.9" customHeight="1" s="24"/>
+    <row r="20" ht="6.85" customHeight="1" s="24"/>
+    <row r="21" ht="6.85" customHeight="1" s="24"/>
+    <row r="22" ht="6.85" customHeight="1" s="24"/>
+    <row r="23" ht="6.85" customHeight="1" s="24"/>
+    <row r="24" ht="6.85" customHeight="1" s="24"/>
+    <row r="25" ht="6.85" customHeight="1" s="24"/>
+    <row r="26" ht="6.9" customHeight="1" s="24"/>
+    <row r="27" ht="6.85" customHeight="1" s="24"/>
+    <row r="28" ht="6.85" customHeight="1" s="24"/>
+    <row r="29" ht="6.85" customHeight="1" s="24"/>
+    <row r="30" ht="6.85" customHeight="1" s="24"/>
+    <row r="31" ht="6.85" customHeight="1" s="24"/>
+    <row r="32" ht="6.9" customHeight="1" s="24"/>
+    <row r="33" ht="6.85" customHeight="1" s="24"/>
+    <row r="34" ht="6.85" customHeight="1" s="24"/>
+    <row r="35" ht="6.85" customHeight="1" s="24"/>
+    <row r="36" ht="6.85" customHeight="1" s="24"/>
+    <row r="37" ht="6.85" customHeight="1" s="24"/>
+    <row r="38" ht="6.85" customHeight="1" s="24"/>
+    <row r="39" ht="6.9" customHeight="1" s="24"/>
+    <row r="40" ht="6.85" customHeight="1" s="24"/>
+    <row r="41" ht="6.85" customHeight="1" s="24"/>
+    <row r="42" ht="6.85" customHeight="1" s="24"/>
+    <row r="43" ht="6.85" customHeight="1" s="24"/>
+    <row r="44" ht="6.85" customHeight="1" s="24"/>
+    <row r="45" ht="6.85" customHeight="1" s="24"/>
+    <row r="46" ht="6.9" customHeight="1" s="24"/>
+    <row r="47" ht="6.85" customHeight="1" s="24"/>
+    <row r="48" ht="6.85" customHeight="1" s="24"/>
+    <row r="49" ht="6.85" customHeight="1" s="24"/>
+    <row r="50" ht="6.85" customHeight="1" s="24"/>
+    <row r="51" ht="6.85" customHeight="1" s="24"/>
+    <row r="52" ht="6.85" customHeight="1" s="24"/>
+    <row r="53" ht="6.9" customHeight="1" s="24"/>
+    <row r="54" ht="6.85" customHeight="1" s="24"/>
+    <row r="55" ht="6.85" customHeight="1" s="24"/>
+    <row r="56" ht="6.85" customHeight="1" s="24"/>
+    <row r="57" ht="6.85" customHeight="1" s="24"/>
+    <row r="58" ht="6.85" customHeight="1" s="24"/>
+    <row r="59" ht="6.85" customHeight="1" s="24"/>
+    <row r="60" ht="6.9" customHeight="1" s="24"/>
+    <row r="61" ht="6.85" customHeight="1" s="24"/>
+    <row r="62" ht="6.85" customHeight="1" s="24"/>
+    <row r="63" ht="6.85" customHeight="1" s="24"/>
+    <row r="64" ht="6.85" customHeight="1" s="24"/>
+    <row r="65" ht="6.85" customHeight="1" s="24"/>
+    <row r="66" ht="6.85" customHeight="1" s="24"/>
+    <row r="67" ht="6.9" customHeight="1" s="24"/>
+    <row r="68" ht="6.85" customHeight="1" s="24"/>
+    <row r="69" ht="6.85" customHeight="1" s="24"/>
+    <row r="70" ht="6.85" customHeight="1" s="24"/>
+    <row r="71" ht="6.85" customHeight="1" s="24"/>
+    <row r="72" ht="6.85" customHeight="1" s="24"/>
+    <row r="73" ht="6.85" customHeight="1" s="24"/>
+    <row r="74" ht="6.9" customHeight="1" s="24"/>
+    <row r="75" ht="6.85" customHeight="1" s="24"/>
+    <row r="76" ht="6.85" customHeight="1" s="24"/>
+    <row r="77" ht="6.85" customHeight="1" s="24"/>
+    <row r="78" ht="6.85" customHeight="1" s="24"/>
+    <row r="79" ht="6.85" customHeight="1" s="24"/>
+    <row r="80" ht="6.9" customHeight="1" s="24"/>
+    <row r="81" ht="6.85" customHeight="1" s="24"/>
+    <row r="82" ht="6.85" customHeight="1" s="24"/>
+    <row r="83" ht="6.85" customHeight="1" s="24"/>
+    <row r="84" ht="6.85" customHeight="1" s="24"/>
+    <row r="85" ht="6.85" customHeight="1" s="24"/>
+    <row r="86" ht="6.85" customHeight="1" s="24"/>
+    <row r="87" ht="6.9" customHeight="1" s="24"/>
+    <row r="88" ht="6.85" customHeight="1" s="24"/>
+    <row r="89" ht="6.85" customHeight="1" s="24"/>
+    <row r="90" ht="6.85" customHeight="1" s="24"/>
+    <row r="91" ht="6.85" customHeight="1" s="24"/>
+    <row r="92" ht="6.85" customHeight="1" s="24"/>
+    <row r="93" ht="6.85" customHeight="1" s="24"/>
+    <row r="94" ht="6.9" customHeight="1" s="24"/>
+    <row r="95" ht="6.85" customHeight="1" s="24"/>
+    <row r="96" ht="6.85" customHeight="1" s="24"/>
+    <row r="97" ht="6.85" customHeight="1" s="24"/>
+    <row r="98" ht="6.85" customHeight="1" s="24"/>
+    <row r="99" ht="6.85" customHeight="1" s="24"/>
+    <row r="100" ht="6.85" customHeight="1" s="24"/>
+    <row r="101" ht="6.9" customHeight="1" s="24"/>
+    <row r="102" ht="6.85" customHeight="1" s="24"/>
+    <row r="103" ht="6.85" customHeight="1" s="24"/>
+    <row r="104" ht="6.85" customHeight="1" s="24"/>
+    <row r="105" ht="6.85" customHeight="1" s="24"/>
+    <row r="106" ht="6.85" customHeight="1" s="24"/>
+    <row r="107" ht="6.85" customHeight="1" s="24"/>
+    <row r="108" ht="6.9" customHeight="1" s="24"/>
+    <row r="109" ht="6.85" customHeight="1" s="24"/>
+    <row r="110" ht="6.85" customHeight="1" s="24"/>
+    <row r="111" ht="6.85" customHeight="1" s="24"/>
+    <row r="112" ht="6.85" customHeight="1" s="24"/>
+    <row r="113" ht="6.85" customHeight="1" s="24"/>
+    <row r="114" ht="6.85" customHeight="1" s="24"/>
+    <row r="115" ht="6.9" customHeight="1" s="24"/>
+    <row r="116" ht="6.85" customHeight="1" s="24"/>
+    <row r="117" ht="6.85" customHeight="1" s="24"/>
+    <row r="118" ht="6.85" customHeight="1" s="24"/>
+    <row r="119" ht="6.85" customHeight="1" s="24"/>
+    <row r="120" ht="6.85" customHeight="1" s="24"/>
+    <row r="121" ht="6.85" customHeight="1" s="24"/>
+    <row r="122" ht="6.9" customHeight="1" s="24"/>
+    <row r="123" ht="6.85" customHeight="1" s="24"/>
+    <row r="124" ht="6.85" customHeight="1" s="24"/>
+    <row r="125" ht="6.85" customHeight="1" s="24"/>
+    <row r="126" ht="6.85" customHeight="1" s="24"/>
+    <row r="127" ht="6.85" customHeight="1" s="24"/>
+    <row r="128" ht="6.9" customHeight="1" s="24"/>
+    <row r="129" ht="6.85" customHeight="1" s="24"/>
+    <row r="130" ht="6.85" customHeight="1" s="24"/>
+    <row r="131" ht="6.85" customHeight="1" s="24"/>
+    <row r="132" ht="6.85" customHeight="1" s="24"/>
+    <row r="133" ht="6.85" customHeight="1" s="24"/>
+    <row r="134" ht="6.85" customHeight="1" s="24"/>
+    <row r="135" ht="6.9" customHeight="1" s="24"/>
+    <row r="136" ht="6.85" customHeight="1" s="24"/>
+    <row r="137" ht="6.85" customHeight="1" s="24"/>
+    <row r="138" ht="6.85" customHeight="1" s="24"/>
+    <row r="139" ht="6.85" customHeight="1" s="24"/>
+    <row r="140" ht="6.85" customHeight="1" s="24"/>
+    <row r="141" ht="6.85" customHeight="1" s="24"/>
+    <row r="142" ht="6.9" customHeight="1" s="24"/>
+    <row r="143" ht="6.85" customHeight="1" s="24"/>
+    <row r="144" ht="6.85" customHeight="1" s="24"/>
+    <row r="145" ht="6.85" customHeight="1" s="24"/>
+    <row r="146" ht="6.85" customHeight="1" s="24"/>
+    <row r="147" ht="6.85" customHeight="1" s="24"/>
+    <row r="148" ht="6.85" customHeight="1" s="24"/>
+    <row r="149" ht="6.9" customHeight="1" s="24"/>
+    <row r="150" ht="6.85" customHeight="1" s="24"/>
+    <row r="151" ht="6.85" customHeight="1" s="24"/>
+    <row r="152" ht="6.85" customHeight="1" s="24"/>
+    <row r="153" ht="6.85" customHeight="1" s="24"/>
+    <row r="154" ht="6.85" customHeight="1" s="24"/>
+    <row r="155" ht="6.85" customHeight="1" s="24"/>
+    <row r="156" ht="6.9" customHeight="1" s="24"/>
+    <row r="157" ht="6.85" customHeight="1" s="24"/>
+    <row r="158" ht="6.85" customHeight="1" s="24"/>
+    <row r="159" ht="6.85" customHeight="1" s="24"/>
+    <row r="160" ht="6.85" customHeight="1" s="24"/>
+    <row r="161" ht="6.85" customHeight="1" s="24"/>
+    <row r="162" ht="6.85" customHeight="1" s="24"/>
+    <row r="163" ht="6.9" customHeight="1" s="24"/>
+    <row r="164" ht="6.85" customHeight="1" s="24"/>
+    <row r="165" ht="6.85" customHeight="1" s="24"/>
+    <row r="166" ht="6.85" customHeight="1" s="24"/>
+    <row r="167" ht="6.85" customHeight="1" s="24"/>
+    <row r="168" ht="6.85" customHeight="1" s="24"/>
+    <row r="169" ht="6.85" customHeight="1" s="24"/>
+    <row r="170" ht="6.9" customHeight="1" s="24"/>
+    <row r="171" ht="6.85" customHeight="1" s="24"/>
+    <row r="172" ht="6.85" customHeight="1" s="24"/>
+    <row r="173" ht="6.85" customHeight="1" s="24"/>
+    <row r="174" ht="6.85" customHeight="1" s="24"/>
+    <row r="175" ht="6.85" customHeight="1" s="24"/>
+    <row r="176" ht="6.9" customHeight="1" s="24"/>
+    <row r="177" ht="6.85" customHeight="1" s="24"/>
+    <row r="178" ht="6.85" customHeight="1" s="24"/>
+    <row r="179" ht="6.85" customHeight="1" s="24"/>
+    <row r="180" ht="6.85" customHeight="1" s="24"/>
+    <row r="181" ht="6.85" customHeight="1" s="24"/>
+    <row r="182" ht="6.85" customHeight="1" s="24"/>
+    <row r="183" ht="6.9" customHeight="1" s="24"/>
+    <row r="184" ht="6.85" customHeight="1" s="24"/>
+    <row r="185" ht="6.85" customHeight="1" s="24"/>
+    <row r="186" ht="6.85" customHeight="1" s="24"/>
+    <row r="187" ht="6.85" customHeight="1" s="24"/>
+    <row r="188" ht="6.85" customHeight="1" s="24"/>
+    <row r="189" ht="6.85" customHeight="1" s="24"/>
+    <row r="190" ht="6.9" customHeight="1" s="24"/>
+    <row r="191" ht="6.85" customHeight="1" s="24"/>
+    <row r="192" ht="6.85" customHeight="1" s="24"/>
+    <row r="193" ht="6.85" customHeight="1" s="24"/>
+    <row r="194" ht="6.85" customHeight="1" s="24"/>
+    <row r="195" ht="6.85" customHeight="1" s="24"/>
+    <row r="196" ht="6.85" customHeight="1" s="24"/>
+    <row r="197" ht="6.9" customHeight="1" s="24"/>
+    <row r="198" ht="6.85" customHeight="1" s="24"/>
+    <row r="199" ht="6.85" customHeight="1" s="24"/>
+    <row r="200" ht="6.85" customHeight="1" s="24"/>
+    <row r="201" ht="6.85" customHeight="1" s="24"/>
+    <row r="202" ht="6.85" customHeight="1" s="24"/>
+    <row r="203" ht="6.85" customHeight="1" s="24"/>
+    <row r="204" ht="6.9" customHeight="1" s="24"/>
+    <row r="205" ht="6.85" customHeight="1" s="24"/>
+    <row r="206" ht="6.85" customHeight="1" s="24"/>
+    <row r="207" ht="6.85" customHeight="1" s="24"/>
+    <row r="208" ht="6.85" customHeight="1" s="24"/>
+    <row r="209" ht="6.85" customHeight="1" s="24"/>
+    <row r="210" ht="6.85" customHeight="1" s="24"/>
+    <row r="211" ht="6.9" customHeight="1" s="24"/>
+    <row r="212" ht="6.85" customHeight="1" s="24"/>
+    <row r="213" ht="6.85" customHeight="1" s="24"/>
+    <row r="214" ht="6.85" customHeight="1" s="24"/>
+    <row r="215" ht="6.85" customHeight="1" s="24"/>
+    <row r="216" ht="6.85" customHeight="1" s="24"/>
+    <row r="217" ht="6.85" customHeight="1" s="24"/>
+    <row r="218" ht="6.9" customHeight="1" s="24"/>
+    <row r="219" ht="6.85" customHeight="1" s="24"/>
+    <row r="220" ht="6.85" customHeight="1" s="24"/>
+    <row r="221" ht="6.85" customHeight="1" s="24"/>
+    <row r="222" ht="6.85" customHeight="1" s="24"/>
+    <row r="223" ht="6.85" customHeight="1" s="24"/>
+    <row r="224" ht="6.9" customHeight="1" s="24"/>
+    <row r="225" ht="6.85" customHeight="1" s="24"/>
+    <row r="226" ht="6.85" customHeight="1" s="24"/>
+    <row r="227" ht="6.85" customHeight="1" s="24"/>
+    <row r="228" ht="6.85" customHeight="1" s="24"/>
+    <row r="229" ht="6.85" customHeight="1" s="24"/>
+    <row r="230" ht="6.85" customHeight="1" s="24"/>
+    <row r="231" ht="6.9" customHeight="1" s="24"/>
+    <row r="232" ht="6.85" customHeight="1" s="24"/>
+    <row r="233" ht="6.85" customHeight="1" s="24"/>
+    <row r="234" ht="6.85" customHeight="1" s="24"/>
+    <row r="235" ht="6.85" customHeight="1" s="24"/>
+    <row r="236" ht="6.85" customHeight="1" s="24"/>
+    <row r="237" ht="6.85" customHeight="1" s="24"/>
+    <row r="238" ht="6.9" customHeight="1" s="24"/>
+    <row r="239" ht="6.85" customHeight="1" s="24"/>
+    <row r="240" ht="6.85" customHeight="1" s="24"/>
+    <row r="241" ht="6.85" customHeight="1" s="24"/>
+    <row r="242" ht="6.85" customHeight="1" s="24"/>
+    <row r="243" ht="6.85" customHeight="1" s="24"/>
+    <row r="244" ht="6.85" customHeight="1" s="24"/>
+    <row r="245" ht="6.9" customHeight="1" s="24"/>
+    <row r="246" ht="6.85" customHeight="1" s="24"/>
+    <row r="247" ht="6.85" customHeight="1" s="24"/>
+    <row r="248" ht="6.85" customHeight="1" s="24"/>
+    <row r="249" ht="6.85" customHeight="1" s="24"/>
+    <row r="250" ht="6.85" customHeight="1" s="24"/>
+    <row r="251" ht="6.85" customHeight="1" s="24"/>
+    <row r="252" ht="6.9" customHeight="1" s="24"/>
+    <row r="253" ht="6.85" customHeight="1" s="24"/>
+    <row r="254" ht="6.85" customHeight="1" s="24"/>
+    <row r="255" ht="6.85" customHeight="1" s="24"/>
+    <row r="256" ht="6.85" customHeight="1" s="24"/>
+    <row r="257" ht="6.85" customHeight="1" s="24"/>
+    <row r="258" ht="6.85" customHeight="1" s="24"/>
+    <row r="259" ht="6.9" customHeight="1" s="24"/>
+    <row r="260" ht="6.85" customHeight="1" s="24"/>
+    <row r="261" ht="6.85" customHeight="1" s="24"/>
+    <row r="262" ht="6.85" customHeight="1" s="24"/>
+    <row r="263" ht="6.85" customHeight="1" s="24"/>
+    <row r="264" ht="6.85" customHeight="1" s="24"/>
+    <row r="265" ht="6.85" customHeight="1" s="24"/>
+    <row r="266" ht="6.9" customHeight="1" s="24"/>
+    <row r="267" ht="6.85" customHeight="1" s="24"/>
+    <row r="268" ht="6.85" customHeight="1" s="24"/>
+    <row r="269" ht="6.85" customHeight="1" s="24"/>
+    <row r="270" ht="6.85" customHeight="1" s="24"/>
+    <row r="271" ht="6.85" customHeight="1" s="24"/>
+    <row r="272" ht="6.9" customHeight="1" s="24"/>
+    <row r="273" ht="6.85" customHeight="1" s="24"/>
+    <row r="274" ht="6.85" customHeight="1" s="24"/>
+    <row r="275" ht="6.85" customHeight="1" s="24"/>
+    <row r="276" ht="6.85" customHeight="1" s="24"/>
+    <row r="277" ht="6.85" customHeight="1" s="24"/>
+    <row r="278" ht="6.85" customHeight="1" s="24"/>
+    <row r="279" ht="6.9" customHeight="1" s="24"/>
+    <row r="280" ht="6.85" customHeight="1" s="24"/>
+    <row r="281" ht="6.85" customHeight="1" s="24"/>
+    <row r="282" ht="6.85" customHeight="1" s="24"/>
+    <row r="283" ht="6.85" customHeight="1" s="24"/>
+    <row r="284" ht="6.85" customHeight="1" s="24"/>
+    <row r="285" ht="6.85" customHeight="1" s="24"/>
+    <row r="286" ht="6.9" customHeight="1" s="24"/>
+    <row r="287" ht="6.85" customHeight="1" s="24"/>
+    <row r="288" ht="6.85" customHeight="1" s="24"/>
+    <row r="289" ht="6.85" customHeight="1" s="24"/>
+    <row r="290" ht="6.85" customHeight="1" s="24"/>
+    <row r="291" ht="6.85" customHeight="1" s="24"/>
+    <row r="292" ht="6.85" customHeight="1" s="24"/>
+    <row r="293" ht="6.9" customHeight="1" s="24"/>
+    <row r="294" ht="6.85" customHeight="1" s="24"/>
+    <row r="295" ht="6.85" customHeight="1" s="24"/>
+    <row r="296" ht="6.85" customHeight="1" s="24"/>
+    <row r="297" ht="6.85" customHeight="1" s="24"/>
+    <row r="298" ht="6.85" customHeight="1" s="24"/>
+    <row r="299" ht="6.85" customHeight="1" s="24"/>
+    <row r="300" ht="6.9" customHeight="1" s="24"/>
+    <row r="301" ht="6.85" customHeight="1" s="24"/>
+    <row r="302" ht="6.85" customHeight="1" s="24"/>
+    <row r="303" ht="6.85" customHeight="1" s="24"/>
+    <row r="304" ht="6.85" customHeight="1" s="24"/>
+    <row r="305" ht="6.85" customHeight="1" s="24"/>
+    <row r="306" ht="6.85" customHeight="1" s="24"/>
+    <row r="307" ht="6.9" customHeight="1" s="24"/>
+    <row r="308" ht="6.85" customHeight="1" s="24"/>
+    <row r="309" ht="6.85" customHeight="1" s="24"/>
+    <row r="310" ht="6.85" customHeight="1" s="24"/>
+    <row r="311" ht="6.85" customHeight="1" s="24"/>
+    <row r="312" ht="6.85" customHeight="1" s="24"/>
+    <row r="313" ht="6.85" customHeight="1" s="24"/>
+    <row r="314" ht="6.9" customHeight="1" s="24"/>
+    <row r="315" ht="6.85" customHeight="1" s="24"/>
+    <row r="316" ht="6.85" customHeight="1" s="24"/>
+    <row r="317" ht="6.85" customHeight="1" s="24"/>
+    <row r="318" ht="6.85" customHeight="1" s="24"/>
+    <row r="319" ht="6.85" customHeight="1" s="24"/>
+    <row r="320" ht="6.9" customHeight="1" s="24"/>
+    <row r="321" ht="6.85" customHeight="1" s="24"/>
+    <row r="322" ht="6.85" customHeight="1" s="24"/>
+    <row r="323" ht="6.85" customHeight="1" s="24"/>
+    <row r="324" ht="6.85" customHeight="1" s="24"/>
+    <row r="325" ht="6.85" customHeight="1" s="24"/>
+    <row r="326" ht="6.85" customHeight="1" s="24"/>
+    <row r="327" ht="6.9" customHeight="1" s="24"/>
+    <row r="328" ht="6.85" customHeight="1" s="24"/>
+    <row r="329" ht="6.85" customHeight="1" s="24"/>
+    <row r="330" ht="6.85" customHeight="1" s="24"/>
+    <row r="331" ht="6.85" customHeight="1" s="24"/>
+    <row r="332" ht="6.85" customHeight="1" s="24"/>
+    <row r="333" ht="6.85" customHeight="1" s="24"/>
+    <row r="334" ht="6.9" customHeight="1" s="24"/>
+    <row r="335" ht="6.85" customHeight="1" s="24"/>
+    <row r="336" ht="6.85" customHeight="1" s="24"/>
+    <row r="337" ht="6.85" customHeight="1" s="24"/>
+    <row r="338" ht="6.85" customHeight="1" s="24"/>
+    <row r="339" ht="6.85" customHeight="1" s="24"/>
+    <row r="340" ht="6.85" customHeight="1" s="24"/>
+    <row r="341" ht="6.9" customHeight="1" s="24"/>
+    <row r="342" ht="6.85" customHeight="1" s="24"/>
+    <row r="343" ht="6.85" customHeight="1" s="24"/>
+    <row r="344" ht="6.85" customHeight="1" s="24"/>
+    <row r="345" ht="6.85" customHeight="1" s="24"/>
+    <row r="346" ht="6.85" customHeight="1" s="24"/>
+    <row r="347" ht="6.85" customHeight="1" s="24"/>
+    <row r="348" ht="6.9" customHeight="1" s="24"/>
+    <row r="349" ht="6.85" customHeight="1" s="24"/>
+    <row r="350" ht="6.85" customHeight="1" s="24"/>
+    <row r="351" ht="6.85" customHeight="1" s="24"/>
+    <row r="352" ht="6.85" customHeight="1" s="24"/>
+    <row r="353" ht="6.85" customHeight="1" s="24"/>
+    <row r="354" ht="6.85" customHeight="1" s="24"/>
+    <row r="355" ht="6.9" customHeight="1" s="24"/>
+    <row r="356" ht="6.85" customHeight="1" s="24"/>
+    <row r="357" ht="6.85" customHeight="1" s="24"/>
+    <row r="358" ht="6.85" customHeight="1" s="24"/>
+    <row r="359" ht="6.85" customHeight="1" s="24"/>
+    <row r="360" ht="6.85" customHeight="1" s="24"/>
+    <row r="361" ht="6.85" customHeight="1" s="24"/>
+    <row r="362" ht="6.9" customHeight="1" s="24"/>
+    <row r="363" ht="6.85" customHeight="1" s="24"/>
+    <row r="364" ht="6.85" customHeight="1" s="24"/>
+    <row r="365" ht="6.85" customHeight="1" s="24"/>
+    <row r="366" ht="6.85" customHeight="1" s="24"/>
+    <row r="367" ht="6.85" customHeight="1" s="24"/>
+    <row r="368" ht="6.9" customHeight="1" s="24"/>
+    <row r="369" ht="6.85" customHeight="1" s="24"/>
+    <row r="370" ht="6.85" customHeight="1" s="24"/>
+    <row r="371" ht="6.85" customHeight="1" s="24"/>
+    <row r="372" ht="6.85" customHeight="1" s="24"/>
+    <row r="373" ht="6.85" customHeight="1" s="24"/>
+    <row r="374" ht="6.85" customHeight="1" s="24"/>
+    <row r="375" ht="6.9" customHeight="1" s="24"/>
+    <row r="376" ht="6.85" customHeight="1" s="24"/>
+    <row r="377" ht="6.85" customHeight="1" s="24"/>
+    <row r="378" ht="6.85" customHeight="1" s="24"/>
+    <row r="379" ht="6.85" customHeight="1" s="24"/>
+    <row r="380" ht="6.85" customHeight="1" s="24"/>
+    <row r="381" ht="6.85" customHeight="1" s="24"/>
+    <row r="382" ht="6.9" customHeight="1" s="24"/>
+    <row r="383" ht="6.85" customHeight="1" s="24"/>
+    <row r="384" ht="6.85" customHeight="1" s="24"/>
+    <row r="385" ht="6.85" customHeight="1" s="24"/>
+    <row r="386" ht="6.85" customHeight="1" s="24"/>
+    <row r="387" ht="6.85" customHeight="1" s="24"/>
+    <row r="388" ht="6.85" customHeight="1" s="24"/>
+    <row r="389" ht="6.9" customHeight="1" s="24"/>
+    <row r="390" ht="6.85" customHeight="1" s="24"/>
+    <row r="391" ht="6.85" customHeight="1" s="24"/>
+    <row r="392" ht="6.85" customHeight="1" s="24"/>
+    <row r="393" ht="6.85" customHeight="1" s="24"/>
+    <row r="394" ht="6.85" customHeight="1" s="24"/>
+    <row r="395" ht="6.85" customHeight="1" s="24"/>
+    <row r="396" ht="6.9" customHeight="1" s="24"/>
+    <row r="397" ht="6.85" customHeight="1" s="24"/>
+    <row r="398" ht="6.85" customHeight="1" s="24"/>
+    <row r="399" ht="6.85" customHeight="1" s="24"/>
+    <row r="400" ht="6.85" customHeight="1" s="24"/>
+    <row r="401" ht="6.85" customHeight="1" s="24"/>
+    <row r="402" ht="6.85" customHeight="1" s="24"/>
+    <row r="403" ht="6.9" customHeight="1" s="24"/>
+    <row r="404" ht="6.85" customHeight="1" s="24"/>
+    <row r="405" ht="6.85" customHeight="1" s="24"/>
+    <row r="406" ht="6.85" customHeight="1" s="24"/>
+    <row r="407" ht="6.85" customHeight="1" s="24"/>
+    <row r="408" ht="6.85" customHeight="1" s="24"/>
+    <row r="409" ht="6.85" customHeight="1" s="24"/>
+    <row r="410" ht="6.9" customHeight="1" s="24"/>
+    <row r="411" ht="6.85" customHeight="1" s="24"/>
+    <row r="412" ht="6.85" customHeight="1" s="24"/>
+    <row r="413" ht="6.85" customHeight="1" s="24"/>
+    <row r="414" ht="6.85" customHeight="1" s="24"/>
+    <row r="415" ht="6.85" customHeight="1" s="24"/>
+    <row r="416" ht="6.9" customHeight="1" s="24"/>
+    <row r="417" ht="6.85" customHeight="1" s="24"/>
+    <row r="418" ht="6.85" customHeight="1" s="24"/>
+    <row r="419" ht="6.85" customHeight="1" s="24"/>
+    <row r="420" ht="6.85" customHeight="1" s="24"/>
+    <row r="421" ht="6.85" customHeight="1" s="24"/>
+    <row r="422" ht="6.85" customHeight="1" s="24"/>
+    <row r="423" ht="6.9" customHeight="1" s="24"/>
+    <row r="424" ht="6.85" customHeight="1" s="24"/>
+    <row r="425" ht="6.85" customHeight="1" s="24"/>
+    <row r="426" ht="6.85" customHeight="1" s="24"/>
+    <row r="427" ht="6.85" customHeight="1" s="24"/>
+    <row r="428" ht="6.85" customHeight="1" s="24"/>
+    <row r="429" ht="6.85" customHeight="1" s="24"/>
+    <row r="430" ht="6.9" customHeight="1" s="24"/>
+    <row r="431" ht="6.85" customHeight="1" s="24"/>
+    <row r="432" ht="6.85" customHeight="1" s="24"/>
+    <row r="433" ht="6.85" customHeight="1" s="24"/>
+    <row r="434" ht="6.85" customHeight="1" s="24"/>
+    <row r="435" ht="6.85" customHeight="1" s="24"/>
+    <row r="436" ht="6.85" customHeight="1" s="24"/>
+    <row r="437" ht="6.9" customHeight="1" s="24"/>
+    <row r="438" ht="6.85" customHeight="1" s="24"/>
+    <row r="439" ht="6.85" customHeight="1" s="24"/>
+    <row r="440" ht="6.85" customHeight="1" s="24"/>
+    <row r="441" ht="6.85" customHeight="1" s="24"/>
+    <row r="442" ht="6.85" customHeight="1" s="24"/>
+    <row r="443" ht="6.85" customHeight="1" s="24"/>
+    <row r="444" ht="6.9" customHeight="1" s="24"/>
+    <row r="445" ht="6.85" customHeight="1" s="24"/>
+    <row r="446" ht="6.85" customHeight="1" s="24"/>
+    <row r="447" ht="6.85" customHeight="1" s="24"/>
+    <row r="448" ht="6.85" customHeight="1" s="24"/>
+    <row r="449" ht="6.85" customHeight="1" s="24"/>
+    <row r="450" ht="6.85" customHeight="1" s="24"/>
+    <row r="451" ht="6.9" customHeight="1" s="24"/>
+    <row r="452" ht="6.85" customHeight="1" s="24"/>
+    <row r="453" ht="6.85" customHeight="1" s="24"/>
+    <row r="454" ht="6.85" customHeight="1" s="24"/>
+    <row r="455" ht="6.85" customHeight="1" s="24"/>
+    <row r="456" ht="6.85" customHeight="1" s="24"/>
+    <row r="457" ht="6.85" customHeight="1" s="24"/>
+    <row r="458" ht="6.9" customHeight="1" s="24"/>
+    <row r="459" ht="6.85" customHeight="1" s="24"/>
+    <row r="460" ht="6.85" customHeight="1" s="24"/>
+    <row r="461" ht="6.85" customHeight="1" s="24"/>
+    <row r="462" ht="6.85" customHeight="1" s="24"/>
+    <row r="463" ht="6.85" customHeight="1" s="24"/>
+    <row r="464" ht="6.9" customHeight="1" s="24"/>
+    <row r="465" ht="6.85" customHeight="1" s="24"/>
+    <row r="466" ht="6.85" customHeight="1" s="24"/>
+    <row r="467" ht="6.85" customHeight="1" s="24"/>
+    <row r="468" ht="6.85" customHeight="1" s="24"/>
+    <row r="469" ht="6.85" customHeight="1" s="24"/>
+    <row r="470" ht="6.85" customHeight="1" s="24"/>
+    <row r="471" ht="6.9" customHeight="1" s="24"/>
+    <row r="472" ht="6.85" customHeight="1" s="24"/>
+    <row r="473" ht="6.85" customHeight="1" s="24"/>
+    <row r="474" ht="6.85" customHeight="1" s="24"/>
+    <row r="475" ht="6.85" customHeight="1" s="24"/>
+    <row r="476" ht="6.85" customHeight="1" s="24"/>
+    <row r="477" ht="6.85" customHeight="1" s="24"/>
+    <row r="478" ht="6.9" customHeight="1" s="24"/>
+    <row r="479" ht="6.85" customHeight="1" s="24"/>
+    <row r="480" ht="6.85" customHeight="1" s="24"/>
+    <row r="481" ht="6.85" customHeight="1" s="24"/>
+    <row r="482" ht="6.85" customHeight="1" s="24"/>
+    <row r="483" ht="6.85" customHeight="1" s="24"/>
+    <row r="484" ht="6.85" customHeight="1" s="24"/>
+    <row r="485" ht="6.9" customHeight="1" s="24"/>
+    <row r="486" ht="6.85" customHeight="1" s="24"/>
+    <row r="487" ht="6.85" customHeight="1" s="24"/>
+    <row r="488" ht="6.85" customHeight="1" s="24"/>
+    <row r="489" ht="6.85" customHeight="1" s="24"/>
+    <row r="490" ht="6.85" customHeight="1" s="24"/>
+    <row r="491" ht="6.85" customHeight="1" s="24"/>
+    <row r="492" ht="6.9" customHeight="1" s="24"/>
+    <row r="493" ht="6.85" customHeight="1" s="24"/>
+    <row r="494" ht="6.85" customHeight="1" s="24"/>
+    <row r="495" ht="6.85" customHeight="1" s="24"/>
+    <row r="496" ht="6.85" customHeight="1" s="24"/>
+    <row r="497" ht="6.85" customHeight="1" s="24"/>
+    <row r="498" ht="6.85" customHeight="1" s="24"/>
+    <row r="499" ht="6.9" customHeight="1" s="24"/>
+    <row r="500" ht="6.85" customHeight="1" s="24"/>
+    <row r="501" ht="6.85" customHeight="1" s="24"/>
+    <row r="502" ht="6.85" customHeight="1" s="24"/>
+    <row r="503" ht="6.85" customHeight="1" s="24"/>
+    <row r="504" ht="6.85" customHeight="1" s="24"/>
+    <row r="505" ht="6.85" customHeight="1" s="24"/>
+    <row r="506" ht="6.9" customHeight="1" s="24"/>
+    <row r="507" ht="6.85" customHeight="1" s="24"/>
+    <row r="508" ht="6.85" customHeight="1" s="24"/>
+    <row r="509" ht="6.85" customHeight="1" s="24"/>
+    <row r="510" ht="6.85" customHeight="1" s="24"/>
+    <row r="511" ht="6.85" customHeight="1" s="24"/>
+    <row r="512" ht="6.9" customHeight="1" s="24"/>
+    <row r="513" ht="6.85" customHeight="1" s="24"/>
+    <row r="514" ht="6.85" customHeight="1" s="24"/>
+    <row r="515" ht="6.85" customHeight="1" s="24"/>
+    <row r="516" ht="6.85" customHeight="1" s="24"/>
+    <row r="517" ht="6.85" customHeight="1" s="24"/>
+    <row r="518" ht="6.85" customHeight="1" s="24"/>
+    <row r="519" ht="6.9" customHeight="1" s="24"/>
+    <row r="520" ht="6.85" customHeight="1" s="24"/>
+    <row r="521" ht="6.85" customHeight="1" s="24"/>
+    <row r="522" ht="6.85" customHeight="1" s="24"/>
+    <row r="523" ht="6.85" customHeight="1" s="24"/>
+    <row r="524" ht="6.85" customHeight="1" s="24"/>
+    <row r="525" ht="6.85" customHeight="1" s="24"/>
+    <row r="526" ht="6.9" customHeight="1" s="24"/>
+    <row r="527" ht="6.85" customHeight="1" s="24"/>
+    <row r="528" ht="6.85" customHeight="1" s="24"/>
+    <row r="529" ht="6.85" customHeight="1" s="24"/>
+    <row r="530" ht="6.85" customHeight="1" s="24"/>
+    <row r="531" ht="6.85" customHeight="1" s="24"/>
+    <row r="532" ht="6.85" customHeight="1" s="24"/>
+    <row r="533" ht="6.9" customHeight="1" s="24"/>
+    <row r="534" ht="6.85" customHeight="1" s="24"/>
+    <row r="535" ht="6.85" customHeight="1" s="24"/>
+    <row r="536" ht="6.85" customHeight="1" s="24"/>
+    <row r="537" ht="6.85" customHeight="1" s="24"/>
+    <row r="538" ht="6.85" customHeight="1" s="24"/>
+    <row r="539" ht="6.85" customHeight="1" s="24"/>
+    <row r="540" ht="6.9" customHeight="1" s="24"/>
+    <row r="541" ht="6.85" customHeight="1" s="24"/>
+    <row r="542" ht="6.85" customHeight="1" s="24"/>
+    <row r="543" ht="6.85" customHeight="1" s="24"/>
+    <row r="544" ht="6.85" customHeight="1" s="24"/>
+    <row r="545" ht="6.85" customHeight="1" s="24"/>
+    <row r="546" ht="6.85" customHeight="1" s="24"/>
+    <row r="547" ht="6.9" customHeight="1" s="24"/>
+    <row r="548" ht="6.85" customHeight="1" s="24"/>
+    <row r="549" ht="6.85" customHeight="1" s="24"/>
+    <row r="550" ht="6.85" customHeight="1" s="24"/>
+    <row r="551" ht="6.85" customHeight="1" s="24"/>
+    <row r="552" ht="6.85" customHeight="1" s="24"/>
+    <row r="553" ht="6.85" customHeight="1" s="24"/>
+    <row r="554" ht="6.9" customHeight="1" s="24"/>
+    <row r="555" ht="6.85" customHeight="1" s="24"/>
+    <row r="556" ht="6.85" customHeight="1" s="24"/>
+    <row r="557" ht="6.85" customHeight="1" s="24"/>
+    <row r="558" ht="6.85" customHeight="1" s="24"/>
+    <row r="559" ht="6.85" customHeight="1" s="24"/>
+    <row r="560" ht="6.9" customHeight="1" s="24"/>
+    <row r="561" ht="6.85" customHeight="1" s="24"/>
+    <row r="562" ht="6.85" customHeight="1" s="24"/>
+    <row r="563" ht="6.85" customHeight="1" s="24"/>
+    <row r="564" ht="6.85" customHeight="1" s="24"/>
+    <row r="565" ht="6.85" customHeight="1" s="24"/>
+    <row r="566" ht="6.85" customHeight="1" s="24"/>
+    <row r="567" ht="6.9" customHeight="1" s="24"/>
+    <row r="568" ht="6.85" customHeight="1" s="24"/>
+    <row r="569" ht="6.85" customHeight="1" s="24"/>
+    <row r="570" ht="6.85" customHeight="1" s="24"/>
+    <row r="571" ht="6.85" customHeight="1" s="24"/>
+    <row r="572" ht="6.85" customHeight="1" s="24"/>
+    <row r="573" ht="6.85" customHeight="1" s="24"/>
+    <row r="574" ht="6.9" customHeight="1" s="24"/>
+    <row r="575" ht="6.85" customHeight="1" s="24"/>
+    <row r="576" ht="6.85" customHeight="1" s="24"/>
+    <row r="577" ht="6.85" customHeight="1" s="24"/>
+    <row r="578" ht="6.85" customHeight="1" s="24"/>
+    <row r="579" ht="6.85" customHeight="1" s="24"/>
+    <row r="580" ht="6.85" customHeight="1" s="24"/>
+    <row r="581" ht="6.9" customHeight="1" s="24"/>
+    <row r="582" ht="6.85" customHeight="1" s="24"/>
+    <row r="583" ht="6.85" customHeight="1" s="24"/>
+    <row r="584" ht="6.85" customHeight="1" s="24"/>
+    <row r="585" ht="6.85" customHeight="1" s="24"/>
+    <row r="586" ht="6.85" customHeight="1" s="24"/>
+    <row r="587" ht="6.85" customHeight="1" s="24"/>
+    <row r="588" ht="6.9" customHeight="1" s="24"/>
+    <row r="589" ht="6.85" customHeight="1" s="24"/>
+    <row r="590" ht="6.85" customHeight="1" s="24"/>
+    <row r="591" ht="6.85" customHeight="1" s="24"/>
+    <row r="592" ht="6.85" customHeight="1" s="24"/>
+    <row r="593" ht="6.85" customHeight="1" s="24"/>
+    <row r="594" ht="6.85" customHeight="1" s="24"/>
+    <row r="595" ht="6.9" customHeight="1" s="24"/>
+    <row r="596" ht="6.85" customHeight="1" s="24"/>
+    <row r="597" ht="6.85" customHeight="1" s="24"/>
+    <row r="598" ht="6.85" customHeight="1" s="24"/>
+    <row r="599" ht="6.85" customHeight="1" s="24"/>
+    <row r="600" ht="6.85" customHeight="1" s="24"/>
+    <row r="601" ht="6.85" customHeight="1" s="24"/>
+    <row r="602" ht="6.9" customHeight="1" s="24"/>
+    <row r="603" ht="6.85" customHeight="1" s="24"/>
+    <row r="604" ht="6.85" customHeight="1" s="24"/>
+    <row r="605" ht="6.85" customHeight="1" s="24"/>
+    <row r="606" ht="6.85" customHeight="1" s="24"/>
+    <row r="607" ht="6.85" customHeight="1" s="24"/>
+    <row r="608" ht="6.9" customHeight="1" s="24"/>
+    <row r="609" ht="6.85" customHeight="1" s="24"/>
+    <row r="610" ht="6.85" customHeight="1" s="24"/>
+    <row r="611" ht="6.85" customHeight="1" s="24"/>
+    <row r="612" ht="6.85" customHeight="1" s="24"/>
+    <row r="613" ht="6.85" customHeight="1" s="24"/>
+    <row r="614" ht="6.85" customHeight="1" s="24"/>
+    <row r="615" ht="6.9" customHeight="1" s="24"/>
+    <row r="616" ht="6.85" customHeight="1" s="24"/>
+    <row r="617" ht="6.85" customHeight="1" s="24"/>
+    <row r="618" ht="6.85" customHeight="1" s="24"/>
+    <row r="619" ht="6.85" customHeight="1" s="24"/>
+    <row r="620" ht="6.85" customHeight="1" s="24"/>
+    <row r="621" ht="6.85" customHeight="1" s="24"/>
+    <row r="622" ht="6.9" customHeight="1" s="24"/>
+    <row r="623" ht="6.85" customHeight="1" s="24"/>
+    <row r="624" ht="6.85" customHeight="1" s="24"/>
+    <row r="625" ht="6.85" customHeight="1" s="24"/>
+    <row r="626" ht="6.85" customHeight="1" s="24"/>
+    <row r="627" ht="6.85" customHeight="1" s="24"/>
+    <row r="628" ht="6.85" customHeight="1" s="24"/>
+    <row r="629" ht="6.9" customHeight="1" s="24"/>
+    <row r="630" ht="6.85" customHeight="1" s="24"/>
+    <row r="631" ht="6.85" customHeight="1" s="24"/>
+    <row r="632" ht="6.85" customHeight="1" s="24"/>
+    <row r="633" ht="6.85" customHeight="1" s="24"/>
+    <row r="634" ht="6.85" customHeight="1" s="24"/>
+    <row r="635" ht="6.85" customHeight="1" s="24"/>
+    <row r="636" ht="6.9" customHeight="1" s="24"/>
+    <row r="637" ht="6.85" customHeight="1" s="24"/>
+    <row r="638" ht="6.85" customHeight="1" s="24"/>
+    <row r="639" ht="6.85" customHeight="1" s="24"/>
+    <row r="640" ht="6.85" customHeight="1" s="24"/>
+    <row r="641" ht="6.85" customHeight="1" s="24"/>
+    <row r="642" ht="6.85" customHeight="1" s="24"/>
+    <row r="643" ht="6.9" customHeight="1" s="24"/>
+    <row r="644" ht="6.85" customHeight="1" s="24"/>
+    <row r="645" ht="6.85" customHeight="1" s="24"/>
+    <row r="646" ht="6.85" customHeight="1" s="24"/>
+    <row r="647" ht="6.85" customHeight="1" s="24"/>
+    <row r="648" ht="6.85" customHeight="1" s="24"/>
+    <row r="649" ht="6.85" customHeight="1" s="24"/>
+    <row r="650" ht="6.9" customHeight="1" s="24"/>
+    <row r="651" ht="6.85" customHeight="1" s="24"/>
+    <row r="652" ht="6.85" customHeight="1" s="24"/>
+    <row r="653" ht="6.85" customHeight="1" s="24"/>
+    <row r="654" ht="6.85" customHeight="1" s="24"/>
+    <row r="655" ht="6.85" customHeight="1" s="24"/>
+    <row r="656" ht="6.9" customHeight="1" s="24"/>
+    <row r="657" ht="6.85" customHeight="1" s="24"/>
+    <row r="658" ht="6.85" customHeight="1" s="24"/>
+    <row r="659" ht="6.85" customHeight="1" s="24"/>
+    <row r="660" ht="6.85" customHeight="1" s="24"/>
+    <row r="661" ht="6.85" customHeight="1" s="24"/>
+    <row r="662" ht="6.85" customHeight="1" s="24"/>
+    <row r="663" ht="6.9" customHeight="1" s="24"/>
+    <row r="664" ht="6.85" customHeight="1" s="24"/>
+    <row r="665" ht="6.85" customHeight="1" s="24"/>
+    <row r="666" ht="6.85" customHeight="1" s="24"/>
+    <row r="667" ht="6.85" customHeight="1" s="24"/>
+    <row r="668" ht="6.85" customHeight="1" s="24"/>
+    <row r="669" ht="6.85" customHeight="1" s="24"/>
+    <row r="670" ht="6.9" customHeight="1" s="24"/>
+    <row r="671" ht="6.85" customHeight="1" s="24"/>
+    <row r="672" ht="6.85" customHeight="1" s="24"/>
+    <row r="673" ht="6.85" customHeight="1" s="24"/>
+    <row r="674" ht="6.85" customHeight="1" s="24"/>
+    <row r="675" ht="6.85" customHeight="1" s="24"/>
+    <row r="676" ht="6.85" customHeight="1" s="24"/>
+    <row r="677" ht="6.9" customHeight="1" s="24"/>
+    <row r="678" ht="6.85" customHeight="1" s="24"/>
+    <row r="679" ht="6.85" customHeight="1" s="24"/>
+    <row r="680" ht="6.85" customHeight="1" s="24"/>
+    <row r="681" ht="6.85" customHeight="1" s="24"/>
+    <row r="682" ht="6.85" customHeight="1" s="24"/>
+    <row r="683" ht="6.85" customHeight="1" s="24"/>
+    <row r="684" ht="6.9" customHeight="1" s="24"/>
+    <row r="685" ht="6.85" customHeight="1" s="24"/>
+    <row r="686" ht="6.85" customHeight="1" s="24"/>
+    <row r="687" ht="6.85" customHeight="1" s="24"/>
+    <row r="688" ht="6.85" customHeight="1" s="24"/>
+    <row r="689" ht="6.85" customHeight="1" s="24"/>
+    <row r="690" ht="6.85" customHeight="1" s="24"/>
+    <row r="691" ht="6.9" customHeight="1" s="24"/>
+    <row r="692" ht="6.85" customHeight="1" s="24"/>
+    <row r="693" ht="6.85" customHeight="1" s="24"/>
+    <row r="694" ht="6.85" customHeight="1" s="24"/>
+    <row r="695" ht="6.85" customHeight="1" s="24"/>
+    <row r="696" ht="6.85" customHeight="1" s="24"/>
+    <row r="697" ht="6.85" customHeight="1" s="24"/>
+    <row r="698" ht="6.9" customHeight="1" s="24"/>
+    <row r="699" ht="6.85" customHeight="1" s="24"/>
+    <row r="700" ht="6.85" customHeight="1" s="24"/>
+    <row r="701" ht="6.85" customHeight="1" s="24"/>
+    <row r="702" ht="6.85" customHeight="1" s="24"/>
+    <row r="703" ht="6.85" customHeight="1" s="24"/>
+    <row r="704" ht="6.9" customHeight="1" s="24"/>
+    <row r="705" ht="6.85" customHeight="1" s="24"/>
+    <row r="706" ht="6.85" customHeight="1" s="24"/>
+    <row r="707" ht="6.85" customHeight="1" s="24"/>
+    <row r="708" ht="6.85" customHeight="1" s="24"/>
+    <row r="709" ht="6.85" customHeight="1" s="24"/>
+    <row r="710" ht="6.85" customHeight="1" s="24"/>
+    <row r="711" ht="6.9" customHeight="1" s="24"/>
+    <row r="712" ht="6.85" customHeight="1" s="24"/>
+    <row r="713" ht="6.85" customHeight="1" s="24"/>
+    <row r="714" ht="6.85" customHeight="1" s="24"/>
+    <row r="715" ht="6.85" customHeight="1" s="24"/>
+    <row r="716" ht="6.85" customHeight="1" s="24"/>
+    <row r="717" ht="6.85" customHeight="1" s="24"/>
+    <row r="718" ht="6.9" customHeight="1" s="24"/>
+    <row r="719" ht="6.85" customHeight="1" s="24"/>
+    <row r="720" ht="6.85" customHeight="1" s="24"/>
+    <row r="721" ht="6.85" customHeight="1" s="24"/>
+    <row r="722" ht="6.85" customHeight="1" s="24"/>
+    <row r="723" ht="6.85" customHeight="1" s="24"/>
+    <row r="724" ht="6.85" customHeight="1" s="24"/>
+    <row r="725" ht="6.9" customHeight="1" s="24"/>
+    <row r="726" ht="6.85" customHeight="1" s="24"/>
+    <row r="727" ht="6.85" customHeight="1" s="24"/>
+    <row r="728" ht="6.85" customHeight="1" s="24"/>
+    <row r="729" ht="6.85" customHeight="1" s="24"/>
+    <row r="730" ht="6.85" customHeight="1" s="24"/>
+    <row r="731" ht="6.85" customHeight="1" s="24"/>
+    <row r="732" ht="6.9" customHeight="1" s="24"/>
+    <row r="733" ht="6.85" customHeight="1" s="24"/>
+    <row r="734" ht="6.85" customHeight="1" s="24"/>
+    <row r="735" ht="6.85" customHeight="1" s="24"/>
+    <row r="736" ht="6.85" customHeight="1" s="24"/>
+    <row r="737" ht="6.85" customHeight="1" s="24"/>
+    <row r="738" ht="6.85" customHeight="1" s="24"/>
+    <row r="739" ht="6.9" customHeight="1" s="24"/>
+    <row r="740" ht="6.85" customHeight="1" s="24"/>
+    <row r="741" ht="6.85" customHeight="1" s="24"/>
+    <row r="742" ht="6.85" customHeight="1" s="24"/>
+    <row r="743" ht="6.85" customHeight="1" s="24"/>
+    <row r="744" ht="6.85" customHeight="1" s="24"/>
+    <row r="745" ht="6.85" customHeight="1" s="24"/>
+    <row r="746" ht="6.9" customHeight="1" s="24"/>
+    <row r="747" ht="6.85" customHeight="1" s="24"/>
+    <row r="748" ht="6.85" customHeight="1" s="24"/>
+    <row r="749" ht="6.85" customHeight="1" s="24"/>
+    <row r="750" ht="6.85" customHeight="1" s="24"/>
+    <row r="751" ht="6.85" customHeight="1" s="24"/>
+    <row r="752" ht="6.9" customHeight="1" s="24"/>
+    <row r="753" ht="6.85" customHeight="1" s="24"/>
+    <row r="754" ht="6.85" customHeight="1" s="24"/>
+    <row r="755" ht="6.85" customHeight="1" s="24"/>
+    <row r="756" ht="6.85" customHeight="1" s="24"/>
+    <row r="757" ht="6.85" customHeight="1" s="24"/>
+    <row r="758" ht="6.85" customHeight="1" s="24"/>
+    <row r="759" ht="6.9" customHeight="1" s="24"/>
+    <row r="760" ht="6.85" customHeight="1" s="24"/>
+    <row r="761" ht="6.85" customHeight="1" s="24"/>
+    <row r="762" ht="6.85" customHeight="1" s="24"/>
+    <row r="763" ht="6.85" customHeight="1" s="24"/>
+    <row r="764" ht="6.85" customHeight="1" s="24"/>
+    <row r="765" ht="6.85" customHeight="1" s="24"/>
+    <row r="766" ht="6.9" customHeight="1" s="24"/>
+    <row r="767" ht="6.85" customHeight="1" s="24"/>
+    <row r="768" ht="6.85" customHeight="1" s="24"/>
+    <row r="769" ht="6.85" customHeight="1" s="24"/>
+    <row r="770" ht="6.85" customHeight="1" s="24"/>
+    <row r="771" ht="6.85" customHeight="1" s="24"/>
+    <row r="772" ht="6.85" customHeight="1" s="24"/>
+    <row r="773" ht="6.9" customHeight="1" s="24"/>
+    <row r="774" ht="6.85" customHeight="1" s="24"/>
+    <row r="775" ht="6.85" customHeight="1" s="24"/>
+    <row r="776" ht="6.85" customHeight="1" s="24"/>
+    <row r="777" ht="6.85" customHeight="1" s="24"/>
+    <row r="778" ht="6.85" customHeight="1" s="24"/>
+    <row r="779" ht="6.85" customHeight="1" s="24"/>
+    <row r="780" ht="6.9" customHeight="1" s="24"/>
+    <row r="781" ht="6.85" customHeight="1" s="24"/>
+    <row r="782" ht="6.85" customHeight="1" s="24"/>
+    <row r="783" ht="6.85" customHeight="1" s="24"/>
+    <row r="784" ht="6.85" customHeight="1" s="24"/>
+    <row r="785" ht="6.85" customHeight="1" s="24"/>
+    <row r="786" ht="6.85" customHeight="1" s="24"/>
+    <row r="787" ht="6.9" customHeight="1" s="24"/>
+    <row r="788" ht="6.85" customHeight="1" s="24"/>
+    <row r="789" ht="6.85" customHeight="1" s="24"/>
+    <row r="790" ht="6.85" customHeight="1" s="24"/>
+    <row r="791" ht="6.85" customHeight="1" s="24"/>
+    <row r="792" ht="6.85" customHeight="1" s="24"/>
+    <row r="793" ht="6.85" customHeight="1" s="24"/>
+    <row r="794" ht="6.9" customHeight="1" s="24"/>
+    <row r="795" ht="6.85" customHeight="1" s="24"/>
+    <row r="796" ht="6.85" customHeight="1" s="24"/>
+    <row r="797" ht="6.85" customHeight="1" s="24"/>
+    <row r="798" ht="6.85" customHeight="1" s="24"/>
+    <row r="799" ht="6.85" customHeight="1" s="24"/>
+    <row r="800" ht="6.9" customHeight="1" s="24"/>
+    <row r="801" ht="6.85" customHeight="1" s="24"/>
+    <row r="802" ht="6.85" customHeight="1" s="24"/>
+    <row r="803" ht="6.85" customHeight="1" s="24"/>
+    <row r="804" ht="6.85" customHeight="1" s="24"/>
+    <row r="805" ht="6.85" customHeight="1" s="24"/>
+    <row r="806" ht="6.85" customHeight="1" s="24"/>
+    <row r="807" ht="6.9" customHeight="1" s="24"/>
+    <row r="808" ht="6.85" customHeight="1" s="24"/>
+    <row r="809" ht="6.85" customHeight="1" s="24"/>
+    <row r="810" ht="6.85" customHeight="1" s="24"/>
+    <row r="811" ht="6.85" customHeight="1" s="24"/>
+    <row r="812" ht="6.85" customHeight="1" s="24"/>
+    <row r="813" ht="6.85" customHeight="1" s="24"/>
+    <row r="814" ht="6.9" customHeight="1" s="24"/>
+    <row r="815" ht="6.85" customHeight="1" s="24"/>
+    <row r="816" ht="6.85" customHeight="1" s="24"/>
+    <row r="817" ht="6.85" customHeight="1" s="24"/>
+    <row r="818" ht="6.85" customHeight="1" s="24"/>
+    <row r="819" ht="6.85" customHeight="1" s="24"/>
+    <row r="820" ht="6.85" customHeight="1" s="24"/>
+    <row r="821" ht="6.9" customHeight="1" s="24"/>
+    <row r="822" ht="6.85" customHeight="1" s="24"/>
+    <row r="823" ht="6.85" customHeight="1" s="24"/>
+    <row r="824" ht="6.85" customHeight="1" s="24"/>
+    <row r="825" ht="6.85" customHeight="1" s="24"/>
+    <row r="826" ht="6.85" customHeight="1" s="24"/>
+    <row r="827" ht="6.85" customHeight="1" s="24"/>
+    <row r="828" ht="6.9" customHeight="1" s="24"/>
+    <row r="829" ht="6.85" customHeight="1" s="24"/>
+    <row r="830" ht="6.85" customHeight="1" s="24"/>
+    <row r="831" ht="6.85" customHeight="1" s="24"/>
+    <row r="832" ht="6.85" customHeight="1" s="24"/>
+    <row r="833" ht="6.85" customHeight="1" s="24"/>
+    <row r="834" ht="6.85" customHeight="1" s="24"/>
+    <row r="835" ht="6.9" customHeight="1" s="24"/>
+    <row r="836" ht="6.85" customHeight="1" s="24"/>
+    <row r="837" ht="6.85" customHeight="1" s="24"/>
+    <row r="838" ht="6.85" customHeight="1" s="24"/>
+    <row r="839" ht="6.85" customHeight="1" s="24"/>
+    <row r="840" ht="6.85" customHeight="1" s="24"/>
+    <row r="841" ht="6.85" customHeight="1" s="24"/>
+    <row r="842" ht="6.9" customHeight="1" s="24"/>
+    <row r="843" ht="6.85" customHeight="1" s="24"/>
+    <row r="844" ht="6.85" customHeight="1" s="24"/>
+    <row r="845" ht="6.85" customHeight="1" s="24"/>
+    <row r="846" ht="6.85" customHeight="1" s="24"/>
+    <row r="847" ht="6.85" customHeight="1" s="24"/>
+    <row r="848" ht="6.9" customHeight="1" s="24"/>
+    <row r="849" ht="6.85" customHeight="1" s="24"/>
+    <row r="850" ht="6.85" customHeight="1" s="24"/>
+    <row r="851" ht="6.85" customHeight="1" s="24"/>
+    <row r="852" ht="6.85" customHeight="1" s="24"/>
+    <row r="853" ht="6.85" customHeight="1" s="24"/>
+    <row r="854" ht="6.85" customHeight="1" s="24"/>
+    <row r="855" ht="6.9" customHeight="1" s="24"/>
+    <row r="856" ht="6.85" customHeight="1" s="24"/>
+    <row r="857" ht="6.85" customHeight="1" s="24"/>
+    <row r="858" ht="6.85" customHeight="1" s="24"/>
+    <row r="859" ht="6.85" customHeight="1" s="24"/>
+    <row r="860" ht="6.85" customHeight="1" s="24"/>
+    <row r="861" ht="6.85" customHeight="1" s="24"/>
+    <row r="862" ht="6.9" customHeight="1" s="24"/>
+    <row r="863" ht="6.85" customHeight="1" s="24"/>
+    <row r="864" ht="6.85" customHeight="1" s="24"/>
+    <row r="865" ht="6.85" customHeight="1" s="24"/>
+    <row r="866" ht="6.85" customHeight="1" s="24"/>
+    <row r="867" ht="6.85" customHeight="1" s="24"/>
+    <row r="868" ht="6.85" customHeight="1" s="24"/>
+    <row r="869" ht="6.9" customHeight="1" s="24"/>
+    <row r="870" ht="6.85" customHeight="1" s="24"/>
+    <row r="871" ht="6.85" customHeight="1" s="24"/>
+    <row r="872" ht="6.85" customHeight="1" s="24"/>
+    <row r="873" ht="6.85" customHeight="1" s="24"/>
+    <row r="874" ht="6.85" customHeight="1" s="24"/>
+    <row r="875" ht="6.85" customHeight="1" s="24"/>
+    <row r="876" ht="6.9" customHeight="1" s="24"/>
+    <row r="877" ht="6.85" customHeight="1" s="24"/>
+    <row r="878" ht="6.85" customHeight="1" s="24"/>
+    <row r="879" ht="6.85" customHeight="1" s="24"/>
+    <row r="880" ht="6.85" customHeight="1" s="24"/>
+    <row r="881" ht="6.85" customHeight="1" s="24"/>
+    <row r="882" ht="6.85" customHeight="1" s="24"/>
+    <row r="883" ht="6.9" customHeight="1" s="24"/>
+    <row r="884" ht="6.85" customHeight="1" s="24"/>
+    <row r="885" ht="6.85" customHeight="1" s="24"/>
+    <row r="886" ht="6.85" customHeight="1" s="24"/>
+    <row r="887" ht="6.85" customHeight="1" s="24"/>
+    <row r="888" ht="6.85" customHeight="1" s="24"/>
+    <row r="889" ht="6.85" customHeight="1" s="24"/>
+    <row r="890" ht="6.9" customHeight="1" s="24"/>
+    <row r="891" ht="6.85" customHeight="1" s="24"/>
+    <row r="892" ht="6.85" customHeight="1" s="24"/>
+    <row r="893" ht="6.85" customHeight="1" s="24"/>
+    <row r="894" ht="6.85" customHeight="1" s="24"/>
+    <row r="895" ht="6.85" customHeight="1" s="24"/>
+    <row r="896" ht="6.9" customHeight="1" s="24"/>
+    <row r="897" ht="6.85" customHeight="1" s="24"/>
+    <row r="898" ht="6.85" customHeight="1" s="24"/>
+    <row r="899" ht="6.85" customHeight="1" s="24"/>
+    <row r="900" ht="6.85" customHeight="1" s="24"/>
+    <row r="901" ht="6.85" customHeight="1" s="24"/>
+    <row r="902" ht="6.85" customHeight="1" s="24"/>
+    <row r="903" ht="6.9" customHeight="1" s="24"/>
+    <row r="904" ht="6.85" customHeight="1" s="24"/>
+    <row r="905" ht="6.85" customHeight="1" s="24"/>
+    <row r="906" ht="6.85" customHeight="1" s="24"/>
+    <row r="907" ht="6.85" customHeight="1" s="24"/>
+    <row r="908" ht="6.85" customHeight="1" s="24"/>
+    <row r="909" ht="6.85" customHeight="1" s="24"/>
+    <row r="910" ht="6.9" customHeight="1" s="24"/>
+    <row r="911" ht="6.85" customHeight="1" s="24"/>
+    <row r="912" ht="6.85" customHeight="1" s="24"/>
+    <row r="913" ht="6.85" customHeight="1" s="24"/>
+    <row r="914" ht="6.85" customHeight="1" s="24"/>
+    <row r="915" ht="6.85" customHeight="1" s="24"/>
+    <row r="916" ht="6.85" customHeight="1" s="24"/>
+    <row r="917" ht="6.9" customHeight="1" s="24"/>
+    <row r="918" ht="6.85" customHeight="1" s="24"/>
+    <row r="919" ht="6.85" customHeight="1" s="24"/>
+    <row r="920" ht="6.85" customHeight="1" s="24"/>
+    <row r="921" ht="6.85" customHeight="1" s="24"/>
+    <row r="922" ht="6.85" customHeight="1" s="24"/>
+    <row r="923" ht="6.85" customHeight="1" s="24"/>
+    <row r="924" ht="6.9" customHeight="1" s="24"/>
+    <row r="925" ht="6.85" customHeight="1" s="24"/>
+    <row r="926" ht="6.85" customHeight="1" s="24"/>
+    <row r="927" ht="6.85" customHeight="1" s="24"/>
+    <row r="928" ht="6.85" customHeight="1" s="24"/>
+    <row r="929" ht="6.85" customHeight="1" s="24"/>
+    <row r="930" ht="6.85" customHeight="1" s="24"/>
+    <row r="931" ht="6.9" customHeight="1" s="24"/>
+    <row r="932" ht="6.85" customHeight="1" s="24"/>
+    <row r="933" ht="6.85" customHeight="1" s="24"/>
+    <row r="934" ht="6.85" customHeight="1" s="24"/>
+    <row r="935" ht="6.85" customHeight="1" s="24"/>
+    <row r="936" ht="6.85" customHeight="1" s="24"/>
+    <row r="937" ht="6.85" customHeight="1" s="24"/>
+    <row r="938" ht="6.9" customHeight="1" s="24"/>
+    <row r="939" ht="6.85" customHeight="1" s="24"/>
+    <row r="940" ht="6.85" customHeight="1" s="24"/>
+    <row r="941" ht="6.85" customHeight="1" s="24"/>
+    <row r="942" ht="6.85" customHeight="1" s="24"/>
+    <row r="943" ht="6.85" customHeight="1" s="24"/>
+    <row r="944" ht="6.9" customHeight="1" s="24"/>
+    <row r="945" ht="6.85" customHeight="1" s="24"/>
+    <row r="946" ht="6.85" customHeight="1" s="24"/>
+    <row r="947" ht="6.85" customHeight="1" s="24"/>
+    <row r="948" ht="6.85" customHeight="1" s="24"/>
+    <row r="949" ht="6.85" customHeight="1" s="24"/>
+    <row r="950" ht="6.85" customHeight="1" s="24"/>
+    <row r="951" ht="6.9" customHeight="1" s="24"/>
+    <row r="952" ht="6.85" customHeight="1" s="24"/>
+    <row r="953" ht="6.85" customHeight="1" s="24"/>
+    <row r="954" ht="6.85" customHeight="1" s="24"/>
+    <row r="955" ht="6.85" customHeight="1" s="24"/>
+    <row r="956" ht="6.85" customHeight="1" s="24"/>
+    <row r="957" ht="6.85" customHeight="1" s="24"/>
+    <row r="958" ht="6.9" customHeight="1" s="24"/>
+    <row r="959" ht="6.85" customHeight="1" s="24"/>
+    <row r="960" ht="6.85" customHeight="1" s="24"/>
+    <row r="961" ht="6.85" customHeight="1" s="24"/>
+    <row r="962" ht="6.85" customHeight="1" s="24"/>
+    <row r="963" ht="6.85" customHeight="1" s="24"/>
+    <row r="964" ht="6.85" customHeight="1" s="24"/>
+    <row r="965" ht="6.9" customHeight="1" s="24"/>
+    <row r="966" ht="6.85" customHeight="1" s="24"/>
+    <row r="967" ht="6.85" customHeight="1" s="24"/>
+    <row r="968" ht="6.85" customHeight="1" s="24"/>
+    <row r="969" ht="6.85" customHeight="1" s="24"/>
+    <row r="970" ht="6.85" customHeight="1" s="24"/>
+    <row r="971" ht="6.85" customHeight="1" s="24"/>
+    <row r="972" ht="6.9" customHeight="1" s="24"/>
+    <row r="973" ht="6.85" customHeight="1" s="24"/>
+    <row r="974" ht="6.85" customHeight="1" s="24"/>
+    <row r="975" ht="6.85" customHeight="1" s="24"/>
+    <row r="976" ht="6.85" customHeight="1" s="24"/>
+    <row r="977" ht="6.85" customHeight="1" s="24"/>
+    <row r="978" ht="6.85" customHeight="1" s="24"/>
+    <row r="979" ht="6.9" customHeight="1" s="24"/>
+    <row r="980" ht="6.85" customHeight="1" s="24"/>
+    <row r="981" ht="6.85" customHeight="1" s="24"/>
+    <row r="982" ht="6.85" customHeight="1" s="24"/>
+    <row r="983" ht="6.85" customHeight="1" s="24"/>
+    <row r="984" ht="6.85" customHeight="1" s="24"/>
+    <row r="985" ht="6.85" customHeight="1" s="24"/>
+    <row r="986" ht="6.9" customHeight="1" s="24"/>
+    <row r="987" ht="6.85" customHeight="1" s="24"/>
+    <row r="988" ht="6.85" customHeight="1" s="24"/>
+    <row r="989" ht="6.85" customHeight="1" s="24"/>
+    <row r="990" ht="6.85" customHeight="1" s="24"/>
+    <row r="991" ht="6.85" customHeight="1" s="24"/>
+    <row r="992" ht="6.9" customHeight="1" s="24"/>
+    <row r="993" ht="6.85" customHeight="1" s="24"/>
+    <row r="994" ht="6.85" customHeight="1" s="24"/>
+    <row r="995" ht="6.85" customHeight="1" s="24"/>
+    <row r="996" ht="6.85" customHeight="1" s="24"/>
+    <row r="997" ht="6.85" customHeight="1" s="24"/>
+    <row r="998" ht="6.85" customHeight="1" s="24"/>
+    <row r="999" ht="6.9" customHeight="1" s="24"/>
+    <row r="1000" ht="6.85" customHeight="1" s="24"/>
+    <row r="1001" ht="6.85" customHeight="1" s="24"/>
+    <row r="1002" ht="6.85" customHeight="1" s="24"/>
+    <row r="1003" ht="6.85" customHeight="1" s="24"/>
+    <row r="1004" ht="6.85" customHeight="1" s="24"/>
+    <row r="1005" ht="6.85" customHeight="1" s="24"/>
+    <row r="1006" ht="6.9" customHeight="1" s="24"/>
+    <row r="1007" ht="6.85" customHeight="1" s="24"/>
+    <row r="1008" ht="6.85" customHeight="1" s="24"/>
+    <row r="1009" ht="6.85" customHeight="1" s="24"/>
+    <row r="1010" ht="6.85" customHeight="1" s="24"/>
+    <row r="1011" ht="6.85" customHeight="1" s="24"/>
+    <row r="1012" ht="6.85" customHeight="1" s="24"/>
+    <row r="1013" ht="6.9" customHeight="1" s="24"/>
+    <row r="1014" ht="6.85" customHeight="1" s="24"/>
+    <row r="1015" ht="6.85" customHeight="1" s="24"/>
+    <row r="1016" ht="6.85" customHeight="1" s="24"/>
+    <row r="1017" ht="6.85" customHeight="1" s="24"/>
+    <row r="1018" ht="6.85" customHeight="1" s="24"/>
+    <row r="1019" ht="6.85" customHeight="1" s="24"/>
+    <row r="1020" ht="6.9" customHeight="1" s="24"/>
+    <row r="1021" ht="6.85" customHeight="1" s="24"/>
+    <row r="1022" ht="6.85" customHeight="1" s="24"/>
+    <row r="1023" ht="6.85" customHeight="1" s="24"/>
+    <row r="1024" ht="6.85" customHeight="1" s="24"/>
+    <row r="1025" ht="6.85" customHeight="1" s="24"/>
+    <row r="1026" ht="6.85" customHeight="1" s="24"/>
+    <row r="1027" ht="6.9" customHeight="1" s="24"/>
+    <row r="1028" ht="6.85" customHeight="1" s="24"/>
+    <row r="1029" ht="6.85" customHeight="1" s="24"/>
+    <row r="1030" ht="6.85" customHeight="1" s="24"/>
+    <row r="1031" ht="6.85" customHeight="1" s="24"/>
+    <row r="1032" ht="6.85" customHeight="1" s="24"/>
+    <row r="1033" ht="6.85" customHeight="1" s="24"/>
+    <row r="1034" ht="6.9" customHeight="1" s="24"/>
+    <row r="1035" ht="6.85" customHeight="1" s="24"/>
+    <row r="1036" ht="6.85" customHeight="1" s="24"/>
+    <row r="1037" ht="6.85" customHeight="1" s="24"/>
+    <row r="1038" ht="6.85" customHeight="1" s="24"/>
+    <row r="1039" ht="6.85" customHeight="1" s="24"/>
+    <row r="1040" ht="6.9" customHeight="1" s="24"/>
+    <row r="1041" ht="6.85" customHeight="1" s="24"/>
+    <row r="1042" ht="6.85" customHeight="1" s="24"/>
+    <row r="1043" ht="6.85" customHeight="1" s="24"/>
+    <row r="1044" ht="6.85" customHeight="1" s="24"/>
+    <row r="1045" ht="6.85" customHeight="1" s="24"/>
+    <row r="1046" ht="6.85" customHeight="1" s="24"/>
+    <row r="1047" ht="6.9" customHeight="1" s="24"/>
+    <row r="1048" ht="6.85" customHeight="1" s="24"/>
+    <row r="1049" ht="6.85" customHeight="1" s="24"/>
+    <row r="1050" ht="6.85" customHeight="1" s="24"/>
+    <row r="1051" ht="6.85" customHeight="1" s="24"/>
+    <row r="1052" ht="6.85" customHeight="1" s="24"/>
+    <row r="1053" ht="6.85" customHeight="1" s="24"/>
+    <row r="1054" ht="6.9" customHeight="1" s="24"/>
+    <row r="1055" ht="6.85" customHeight="1" s="24"/>
+    <row r="1056" ht="6.85" customHeight="1" s="24"/>
+    <row r="1057" ht="6.85" customHeight="1" s="24"/>
+    <row r="1058" ht="6.85" customHeight="1" s="24"/>
+    <row r="1059" ht="6.85" customHeight="1" s="24"/>
+    <row r="1060" ht="6.85" customHeight="1" s="24"/>
+    <row r="1061" ht="6.9" customHeight="1" s="24"/>
+    <row r="1062" ht="6.85" customHeight="1" s="24"/>
+    <row r="1063" ht="6.85" customHeight="1" s="24"/>
+    <row r="1064" ht="6.85" customHeight="1" s="24"/>
+    <row r="1065" ht="6.85" customHeight="1" s="24"/>
+    <row r="1066" ht="6.85" customHeight="1" s="24"/>
+    <row r="1067" ht="6.85" customHeight="1" s="24"/>
+    <row r="1068" ht="6.9" customHeight="1" s="24"/>
+    <row r="1069" ht="6.85" customHeight="1" s="24"/>
+    <row r="1070" ht="6.8" customHeight="1" s="24"/>
+    <row r="1071" ht="0.05" customHeight="1" s="24"/>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="E1069:G1069"/>
+    <mergeCell ref="H1070:I1070"/>
+    <mergeCell ref="H1069:I1069"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A1069:D1069"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E1067:G1067"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="A1067:D1067"/>
+    <mergeCell ref="A1070:D1070"/>
+    <mergeCell ref="H1067:I1067"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="E1068:G1068"/>
+    <mergeCell ref="H1068:I1068"/>
+    <mergeCell ref="E1070:G1070"/>
+    <mergeCell ref="A1068:D1068"/>
+    <mergeCell ref="I2:I3"/>
+  </mergeCells>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1.83203125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="10.07421875" customWidth="1" style="24" min="2" max="2"/>
+    <col width="0.203125" customWidth="1" style="24" min="3" max="3"/>
+    <col width="16.11328125" customWidth="1" style="24" min="4" max="4"/>
+    <col width="1.5234375" customWidth="1" style="24" min="5" max="5"/>
+    <col width="12.53125" customWidth="1" style="24" min="6" max="6"/>
+    <col width="0.59375" customWidth="1" style="24" min="7" max="7"/>
+    <col width="5.28125" customWidth="1" style="24" min="8" max="8"/>
+    <col width="0.65234375" customWidth="1" style="24" min="9" max="9"/>
+    <col width="3.44140625" customWidth="1" style="24" min="10" max="10"/>
+    <col width="9.5625" customWidth="1" style="24" min="11" max="11"/>
+    <col width="9.2734375" customWidth="1" style="24" min="12" max="12"/>
+    <col width="1.18359375" customWidth="1" style="24" min="13" max="13"/>
+    <col width="10.11328125" customWidth="1" style="24" min="14" max="14"/>
+    <col width="9.00390625" customWidth="1" style="24" min="15" max="15"/>
+    <col width="0.390625" customWidth="1" style="24" min="16" max="16"/>
+    <col width="2.19140625" customWidth="1" style="24" min="17" max="17"/>
+    <col width="0.453125" customWidth="1" style="24" min="18" max="18"/>
+    <col width="2.84375" customWidth="1" style="24" min="19" max="19"/>
+    <col width="14.09375" customWidth="1" style="24" min="20" max="20"/>
+    <col width="3.73046875" customWidth="1" style="24" min="21" max="21"/>
+    <col width="0.1328125" customWidth="1" style="24" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="8.75" customHeight="1" s="24">
+      <c r="A1" s="18" t="str"/>
+      <c r="B1" s="18" t="str"/>
+      <c r="C1" s="18" t="str"/>
+      <c r="D1" s="18" t="str"/>
+      <c r="E1" s="18" t="str"/>
+      <c r="F1" s="18" t="str"/>
+      <c r="G1" s="18" t="str"/>
+      <c r="H1" s="18" t="str"/>
+      <c r="I1" s="18" t="str"/>
+      <c r="J1" s="18" t="str"/>
+      <c r="K1" s="18" t="str"/>
+      <c r="L1" s="18" t="str"/>
+      <c r="M1" s="18" t="str"/>
+      <c r="N1" s="18" t="str"/>
+      <c r="O1" s="18" t="str"/>
+      <c r="P1" s="18" t="str"/>
+      <c r="Q1" s="18" t="str"/>
+      <c r="R1" s="18" t="str"/>
+      <c r="S1" s="18" t="str"/>
+      <c r="T1" s="18" t="str"/>
+      <c r="U1" s="18" t="str"/>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>65491674</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>VASELINE GH SPF 50 VCT SERUM 2X6X200ML</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>4</v>
-      </c>
+    <row r="2" ht="20.2" customHeight="1" s="24">
+      <c r="A2" s="18" t="str"/>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>00000000~NAMA DISTRIBUTOR (contoh)</t>
+        </is>
+      </c>
+      <c r="T2" s="18" t="str"/>
+      <c r="U2" s="18" t="str"/>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Catatan: baris 1-2 adalah header (jangan diubah struktur/urutan kolomnya).</t>
-        </is>
-      </c>
+    <row r="3" ht="0.05" customHeight="1" s="24">
+      <c r="A3" s="18" t="str"/>
+      <c r="B3" s="18" t="str"/>
+      <c r="C3" s="18" t="str"/>
+      <c r="D3" s="18" t="str"/>
+      <c r="E3" s="18" t="str"/>
+      <c r="F3" s="18" t="str"/>
+      <c r="G3" s="18" t="str"/>
+      <c r="H3" s="18" t="str"/>
+      <c r="I3" s="18" t="str"/>
+      <c r="J3" s="18" t="str"/>
+      <c r="K3" s="18" t="str"/>
+      <c r="L3" s="18" t="str"/>
+      <c r="M3" s="18" t="str"/>
+      <c r="N3" s="18" t="str"/>
+      <c r="O3" s="18" t="str"/>
+      <c r="P3" s="18" t="str"/>
+      <c r="Q3" s="18" t="str"/>
+      <c r="R3" s="18" t="str"/>
+      <c r="S3" s="18" t="str"/>
+      <c r="T3" s="18" t="str"/>
+      <c r="U3" s="18" t="str"/>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Baris kuning (3-7) contoh format -- hapus/timpa dengan data asli distributor sebelum upload.</t>
-        </is>
-      </c>
+    <row r="4" ht="12" customHeight="1" s="24">
+      <c r="A4" s="18" t="str"/>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Distributor Stock Report</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="str"/>
+      <c r="L4" s="18" t="str"/>
+      <c r="M4" s="18" t="str"/>
+      <c r="N4" s="18" t="str"/>
+      <c r="O4" s="18" t="str"/>
+      <c r="P4" s="18" t="str"/>
+      <c r="Q4" s="18" t="str"/>
+      <c r="R4" s="18" t="str"/>
+      <c r="S4" s="18" t="str"/>
+      <c r="T4" s="18" t="str"/>
+      <c r="U4" s="18" t="str"/>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>PCODE harus sama dengan PC Code di daftar SKU wajib (bukan barcode).</t>
-        </is>
-      </c>
+    <row r="5" ht="10.65" customHeight="1" s="24">
+      <c r="A5" s="18" t="str"/>
+      <c r="B5" s="18" t="str"/>
+      <c r="C5" s="18" t="str"/>
+      <c r="D5" s="18" t="str"/>
+      <c r="E5" s="18" t="str"/>
+      <c r="F5" s="18" t="str"/>
+      <c r="G5" s="18" t="str"/>
+      <c r="H5" s="18" t="str"/>
+      <c r="I5" s="18" t="str"/>
+      <c r="J5" s="18" t="str"/>
+      <c r="K5" s="18" t="str"/>
+      <c r="L5" s="18" t="str"/>
+      <c r="M5" s="18" t="str"/>
+      <c r="N5" s="18" t="str"/>
+      <c r="O5" s="18" t="str"/>
+      <c r="P5" s="18" t="str"/>
+      <c r="Q5" s="18" t="str"/>
+      <c r="R5" s="18" t="str"/>
+      <c r="S5" s="18" t="str"/>
+      <c r="T5" s="18" t="str"/>
+      <c r="U5" s="18" t="str"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="24">
+      <c r="A6" s="18" t="str"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Tanggal:</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="str"/>
+      <c r="D6" s="28" t="n">
+        <v>46325</v>
+      </c>
+      <c r="E6" s="18" t="str"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>Print Date Time:</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="str"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>10/30/2026 4:34:42 PM</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="str"/>
+      <c r="M6" s="18" t="str"/>
+      <c r="N6" s="18" t="str"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>Status Stock:</t>
+        </is>
+      </c>
+      <c r="R6" s="18" t="str"/>
+      <c r="S6" s="23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="U6" s="18" t="str"/>
+    </row>
+    <row r="7" ht="1.8" customHeight="1" s="24">
+      <c r="A7" s="18" t="str"/>
+      <c r="B7" s="18" t="str"/>
+      <c r="C7" s="18" t="str"/>
+      <c r="D7" s="18" t="str"/>
+      <c r="E7" s="18" t="str"/>
+      <c r="F7" s="18" t="str"/>
+      <c r="G7" s="18" t="str"/>
+      <c r="H7" s="18" t="str"/>
+      <c r="I7" s="18" t="str"/>
+      <c r="J7" s="18" t="str"/>
+      <c r="K7" s="18" t="str"/>
+      <c r="L7" s="18" t="str"/>
+      <c r="M7" s="18" t="str"/>
+      <c r="N7" s="18" t="str"/>
+      <c r="O7" s="18" t="str"/>
+      <c r="P7" s="18" t="str"/>
+      <c r="Q7" s="18" t="str"/>
+      <c r="R7" s="18" t="str"/>
+      <c r="S7" s="18" t="str"/>
+      <c r="T7" s="18" t="str"/>
+      <c r="U7" s="18" t="str"/>
+    </row>
+    <row r="8" ht="0.9" customHeight="1" s="24">
+      <c r="A8" s="18" t="str"/>
+      <c r="B8" s="18" t="str"/>
+      <c r="C8" s="18" t="str"/>
+      <c r="D8" s="18" t="str"/>
+      <c r="E8" s="18" t="str"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Hirarki Produk :</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="str"/>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="str"/>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t>Pilihan Level Hirarki :</t>
+        </is>
+      </c>
+      <c r="P8" s="18" t="str"/>
+      <c r="Q8" s="23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="U8" s="18" t="str"/>
+    </row>
+    <row r="9" ht="17.1" customHeight="1" s="24">
+      <c r="A9" s="18" t="str"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Gudang :</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="str"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Gudang Utama</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="str"/>
+      <c r="I9" s="18" t="str"/>
+      <c r="M9" s="18" t="str"/>
+      <c r="P9" s="18" t="str"/>
+      <c r="U9" s="18" t="str"/>
+    </row>
+    <row r="10" ht="0.9" customHeight="1" s="24">
+      <c r="A10" s="18" t="str"/>
+      <c r="C10" s="18" t="str"/>
+      <c r="E10" s="18" t="str"/>
+      <c r="F10" s="18" t="str"/>
+      <c r="G10" s="18" t="str"/>
+      <c r="H10" s="18" t="str"/>
+      <c r="I10" s="18" t="str"/>
+      <c r="J10" s="18" t="str"/>
+      <c r="K10" s="18" t="str"/>
+      <c r="L10" s="18" t="str"/>
+      <c r="M10" s="18" t="str"/>
+      <c r="N10" s="18" t="str"/>
+      <c r="O10" s="18" t="str"/>
+      <c r="P10" s="18" t="str"/>
+      <c r="Q10" s="18" t="str"/>
+      <c r="R10" s="18" t="str"/>
+      <c r="S10" s="18" t="str"/>
+      <c r="T10" s="18" t="str"/>
+      <c r="U10" s="18" t="str"/>
+    </row>
+    <row r="11" ht="18.4" customHeight="1" s="24">
+      <c r="A11" s="18" t="str"/>
+      <c r="B11" s="18" t="str"/>
+      <c r="C11" s="18" t="str"/>
+      <c r="D11" s="18" t="str"/>
+      <c r="E11" s="18" t="str"/>
+      <c r="F11" s="18" t="str"/>
+      <c r="G11" s="18" t="str"/>
+      <c r="H11" s="18" t="str"/>
+      <c r="I11" s="18" t="str"/>
+      <c r="J11" s="18" t="str"/>
+      <c r="K11" s="18" t="str"/>
+      <c r="L11" s="18" t="str"/>
+      <c r="M11" s="18" t="str"/>
+      <c r="N11" s="18" t="str"/>
+      <c r="O11" s="18" t="str"/>
+      <c r="P11" s="18" t="str"/>
+      <c r="Q11" s="18" t="str"/>
+      <c r="R11" s="18" t="str"/>
+      <c r="S11" s="18" t="str"/>
+      <c r="T11" s="18" t="str"/>
+      <c r="U11" s="18" t="str"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D1:F1"/>
+  <mergeCells count="11">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="B2:S2"/>
+    <mergeCell ref="Q8:T9"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="F8:H9"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="J8:L9"/>
+    <mergeCell ref="N8:O9"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>